--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_aysen.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>33.70567868786171</v>
+      </c>
+      <c r="C2">
         <v>22.48477343374864</v>
-      </c>
-      <c r="C2">
-        <v>33.70567868786171</v>
       </c>
       <c r="D2">
         <v>4.447454198044285</v>
       </c>
       <c r="E2">
-        <v>14.39574130705629</v>
+        <v>21.57985858291669</v>
       </c>
       <c r="F2">
         <v>64.02440011002702</v>
       </c>
       <c r="G2">
-        <v>21.57985858291669</v>
+        <v>14.39574130705629</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>31.19266055045872</v>
+      </c>
+      <c r="C3">
         <v>41.05504587155963</v>
-      </c>
-      <c r="C3">
-        <v>31.19266055045872</v>
       </c>
       <c r="D3">
         <v>2.435754189944134</v>
       </c>
       <c r="E3">
-        <v>23.83488681757656</v>
+        <v>18.10918774966711</v>
       </c>
       <c r="F3">
         <v>58.05592543275633</v>
       </c>
       <c r="G3">
-        <v>18.10918774966711</v>
+        <v>23.83488681757656</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>33.45446020396202</v>
+      </c>
+      <c r="C4">
         <v>21.9317782206072</v>
-      </c>
-      <c r="C4">
-        <v>33.45446020396202</v>
       </c>
       <c r="D4">
         <v>4.559593800106895</v>
       </c>
       <c r="E4">
-        <v>14.11436330718165</v>
+        <v>21.52987326493663</v>
       </c>
       <c r="F4">
         <v>64.35576342788171</v>
       </c>
       <c r="G4">
-        <v>21.52987326493663</v>
+        <v>14.11436330718165</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>35.21046643913538</v>
+      </c>
+      <c r="C5">
         <v>21.55858930602958</v>
-      </c>
-      <c r="C5">
-        <v>35.21046643913538</v>
       </c>
       <c r="D5">
         <v>4.638522427440633</v>
       </c>
       <c r="E5">
-        <v>13.75181422351234</v>
+        <v>22.46008708272859</v>
       </c>
       <c r="F5">
         <v>63.78809869375907</v>
       </c>
       <c r="G5">
-        <v>22.46008708272859</v>
+        <v>13.75181422351234</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>33.96404919583728</v>
+      </c>
+      <c r="C6">
         <v>17.21854304635762</v>
-      </c>
-      <c r="C6">
-        <v>33.96404919583728</v>
       </c>
       <c r="D6">
         <v>5.807692307692307</v>
       </c>
       <c r="E6">
-        <v>11.3892365456821</v>
+        <v>22.46558197747184</v>
       </c>
       <c r="F6">
         <v>66.14518147684606</v>
       </c>
       <c r="G6">
-        <v>22.46558197747184</v>
+        <v>11.3892365456821</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>33.27556325823224</v>
+      </c>
+      <c r="C7">
         <v>25.08665511265164</v>
-      </c>
-      <c r="C7">
-        <v>33.27556325823224</v>
       </c>
       <c r="D7">
         <v>3.986183074265976</v>
       </c>
       <c r="E7">
-        <v>15.84131326949384</v>
+        <v>21.01231190150479</v>
       </c>
       <c r="F7">
         <v>63.14637482900137</v>
       </c>
       <c r="G7">
-        <v>21.01231190150479</v>
+        <v>15.84131326949384</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>37.43718592964824</v>
+      </c>
+      <c r="C8">
         <v>17.8391959798995</v>
-      </c>
-      <c r="C8">
-        <v>37.43718592964824</v>
       </c>
       <c r="D8">
         <v>5.605633802816901</v>
       </c>
       <c r="E8">
-        <v>11.48867313915857</v>
+        <v>24.11003236245955</v>
       </c>
       <c r="F8">
         <v>64.40129449838187</v>
       </c>
       <c r="G8">
-        <v>24.11003236245955</v>
+        <v>11.48867313915857</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>40.88050314465409</v>
+      </c>
+      <c r="C9">
         <v>13.83647798742138</v>
-      </c>
-      <c r="C9">
-        <v>40.88050314465409</v>
       </c>
       <c r="D9">
         <v>7.227272727272728</v>
       </c>
       <c r="E9">
-        <v>8.943089430894307</v>
+        <v>26.42276422764228</v>
       </c>
       <c r="F9">
-        <v>64.63414634146341</v>
+        <v>64.63414634146342</v>
       </c>
       <c r="G9">
-        <v>26.42276422764228</v>
+        <v>8.943089430894309</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.90460018524236</v>
+      </c>
+      <c r="C10">
         <v>34.73294226613152</v>
-      </c>
-      <c r="C10">
-        <v>30.90460018524236</v>
       </c>
       <c r="D10">
         <v>2.879111111111111</v>
       </c>
       <c r="E10">
+        <v>18.65796831314072</v>
+      </c>
+      <c r="F10">
+        <v>60.37278657968313</v>
+      </c>
+      <c r="G10">
         <v>20.96924510717614</v>
-      </c>
-      <c r="F10">
-        <v>60.37278657968314</v>
-      </c>
-      <c r="G10">
-        <v>18.65796831314073</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>31.12062812276945</v>
+      </c>
+      <c r="C11">
         <v>41.89864382583869</v>
-      </c>
-      <c r="C11">
-        <v>31.12062812276945</v>
       </c>
       <c r="D11">
         <v>2.386712095400341</v>
       </c>
       <c r="E11">
-        <v>24.21617161716172</v>
+        <v>17.98679867986798</v>
       </c>
       <c r="F11">
         <v>57.79702970297029</v>
       </c>
       <c r="G11">
-        <v>17.98679867986798</v>
+        <v>24.21617161716172</v>
       </c>
     </row>
   </sheetData>
